--- a/content/Question Bank/Coding Questions/Unit 6 - Lists and Tuples/Unit 6 - Lists and Tuples - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 6 - Lists and Tuples/Unit 6 - Lists and Tuples - Coding Questions.xlsx
@@ -596,13 +596,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Read a line of space-separated numbers and print them sorted from smallest to largest, separated by spaces.
+          <t>At cricket practice, Coach Iyer jots down the runs his opening batsman scored in each recent match. Before the team meeting he wants the scores arranged from smallest to largest, so the batsman's best and worst days are easy to see.
+Read one line of space-separated numbers and print the same numbers sorted from smallest to largest, separated by single spaces.
 ### Input Format
 - Line 1: Space-separated numbers
 ### Output Format
 ```
 1 1 3 4 5
 ```
+### Example Walkthrough
+The sample scores are `3 1 4 1 5`. Arranged from smallest to largest they become 1, 1, 3, 4, 5, so the program prints `1 1 3 4 5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -740,14 +743,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Read a line of space-separated values, then a value. Print 'Yes' if the value is in the list, otherwise print 'No'.
+          <t>The juice stall outside the college gate writes today's available fruits on a small board. Customers keep asking, "Bhaiya, is banana there today?" — so the owner's son wants a program that answers instantly.
+Read a line of space-separated values (the list), then a single value on the next line. Print `Yes` if the value appears anywhere in the list, otherwise print `No`.
 ### Input Format
 - Line 1: Space-separated values
-- Line 2: The value to find
+- Line 2: The value to search for
 ### Output Format
 ```
 Yes
 ```
+### Example Walkthrough
+The sample list is `apple banana cherry` and the value to find is `banana`. Since `banana` is in the list, the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -893,13 +899,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Read a line of space-separated values and print them in reverse order, separated by spaces.
+          <t>Ravi takes the city bus to college every morning, and the bus stops at the same places in a fixed order. On the return trip in the evening, the bus visits exactly the same stops but backwards, and Ravi wants a program that prints the return-trip order.
+Read a line of space-separated values and print them in reverse order — last one first, first one last — separated by single spaces.
 ### Input Format
 - Line 1: Space-separated values
 ### Output Format
 ```
 4 3 2 1
 ```
+### Example Walkthrough
+The sample input is `1 2 3 4`. Reversing the order puts 4 first and 1 last, so the program prints `4 3 2 1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1037,13 +1046,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Read a line of space-separated values and print each distinct value once, keeping the order of first appearance, separated by spaces.
+          <t>At the tech fest registration desk, excited students sometimes sign up two or three times for the same event. Organiser Sneha wants a clean participant list where each entry appears only once, kept in the order people first registered.
+Read a line of space-separated values and print each distinct value exactly once — that is, with all repeats removed — keeping the order in which each value first appeared, separated by spaces.
 ### Input Format
 - Line 1: Space-separated values
 ### Output Format
 ```
 a b c
 ```
+### Example Walkthrough
+The sample input is `a b a c b a`. Reading left to right, `a` appears first, then `b`, then `c`; every later repeat of `a` or `b` is skipped, so the program prints `a b c`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1185,13 +1197,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Read a line of space-separated numbers and print each number squared, in the same order, separated by spaces. Use a list comprehension.
+          <t>Nisha is making flashcards of square numbers to help her younger brother prepare for his maths olympiad. For each number on a card, the back of the card must show that number multiplied by itself.
+Read a line of space-separated numbers and print the square of each number (the number multiplied by itself), in the same order, separated by spaces. Build the squared list using a list comprehension.
 ### Input Format
 - Line 1: Space-separated numbers
 ### Output Format
 ```
 1 4 9
 ```
+### Example Walkthrough
+The sample numbers are `1 2 3`. Squaring each gives 1×1 = 1, 2×2 = 4 and 3×3 = 9, so the program prints `1 4 9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1330,13 +1345,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Read a line of space-separated numbers and print the smallest and largest as a pair in the form (min, max).
+          <t>The hostel warden notes the electricity units consumed by the boys' hostel each day for a week. For his monthly report he only needs the two extremes — the lowest and the highest daily reading — written together as a pair.
+Read a line of space-separated numbers, find the smallest and the largest, and print them as a pair in the exact form `(min, max)` — with parentheses, a comma, and a space after the comma.
 ### Input Format
 - Line 1: Space-separated numbers
 ### Output Format
 ```
 (1, 5)
 ```
+### Example Walkthrough
+In the sample readings `3 1 4 1 5`, the smallest value is 1 and the largest is 5. Printed as a pair, that is `(1, 5)`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1475,14 +1493,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Read two lines, each a set of space-separated numbers. Combine them into one list, sort it from smallest to largest, and print it.
+          <t>At the college fest, two ticket counters each kept their own list of token numbers sold during the day. At closing time, the accounts team needs all the tokens from both counters combined into one single list, arranged from smallest to largest.
+Read two lines, each containing space-separated numbers. Join the two groups into one list, sort it from smallest to largest, and print the numbers separated by spaces.
 ### Input Format
-- Line 1: First set of numbers
-- Line 2: Second set of numbers
+- Line 1: First group of space-separated numbers
+- Line 2: Second group of space-separated numbers
 ### Output Format
 ```
 1 2 3 4
 ```
+### Example Walkthrough
+The sample groups are `3 1` and `4 2`. Combined they form 3, 1, 4, 2, and sorting from smallest to largest gives `1 2 3 4`, which is what the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1628,16 +1649,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Read a grid with R rows and C columns, then print its transpose: the row/column roles swapped, C rows of R values each.
+          <t>Anil stores his class's internal marks in a grid: each row is one student and each column is one subject. His teacher wants the same data flipped around — each row should be one subject instead — so Anil must swap the rows and columns. This flipped grid is called the transpose.
+Read the grid size `R` and `C`, then the `R` rows of the grid. Print the transpose: the first column of the original becomes the first row of the answer, the second column becomes the second row, and so on — giving `C` rows with `R` values each.
 ### Input Format
-- Line 1: R and C separated by a space
-- Next R lines: C space-separated numbers each
+- Line 1: `R` and `C` separated by a space
+- Next `R` lines: `C` space-separated numbers each
 ### Output Format
 ```
 1 4
 2 5
 3 6
 ```
+### Example Walkthrough
+The sample grid has 2 rows and 3 columns: `1 2 3` and `4 5 6`. Its columns, read top to bottom, are (1, 4), (2, 5) and (3, 6), so the program prints the three lines `1 4`, `2 5` and `3 6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1802,16 +1826,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Read N students, each on a line with a name and a score. Print the names in order from highest score to lowest. Keep the original order for students who tie.
+          <t>After the internal exams, Professor Rao wants a merit list pinned on the notice board: student names arranged from the highest scorer down to the lowest. If two students score the same, whoever appeared first in the register stays first.
+Read `N`, then `N` lines each containing a student's name and score. Print only the names, one per line, ordered from highest score to lowest. Students with equal scores keep their original input order.
 ### Input Format
-- Line 1: N
-- Next N lines: 'name score'
+- Line 1: `N`, the number of students
+- Next `N` lines: `name score`
 ### Output Format
 ```
 kabir
 asha
 meera
 ```
+### Example Walkthrough
+In the sample, `kabir` scored 95, `asha` scored 80 and `meera` scored 70. Ordering from highest to lowest score gives `kabir`, then `asha`, then `meera` — printed one name per line.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1978,13 +2005,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Read a line of space-separated numbers and print the product of each adjacent pair, in order, separated by spaces. For '1 2 3 4' the answer is '2 6 12'.
+          <t>Simran is setting a number puzzle for the class magazine. She writes a row of numbers and asks readers to build the next row by multiplying each pair of neighbours — the 1st number times the 2nd, the 2nd times the 3rd, and so on.
+Read a line of space-separated numbers and print the product of every adjacent (neighbouring) pair, in order, separated by spaces. A list of `N` numbers produces `N-1` products.
 ### Input Format
 - Line 1: Space-separated numbers (at least two)
 ### Output Format
 ```
 2 6 12
 ```
+### Example Walkthrough
+The sample row is `1 2 3 4`. The neighbouring products are 1×2 = 2, 2×3 = 6 and 3×4 = 12, so the program prints `2 6 12`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>

--- a/content/Question Bank/Coding Questions/Unit 6 - Lists and Tuples/Unit 6 - Lists and Tuples - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 6 - Lists and Tuples/Unit 6 - Lists and Tuples - Coding Questions.xlsx
@@ -1,13 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH31"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -621,22 +624,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>lists</t>
+          <t>lists-and-tuples</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>list-operations</t>
+          <t>list-methods</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -769,22 +782,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>lists</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>list-operations</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -924,22 +947,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>lists</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>list-operations</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1071,22 +1104,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>lists</t>
+          <t>lists-and-tuples</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>list-operations</t>
+          <t>list-methods</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1222,17 +1265,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>lists</t>
+          <t>lists-and-tuples</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1370,17 +1423,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>lists</t>
+          <t>lists-and-tuples</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1519,22 +1582,32 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>lists</t>
+          <t>lists-and-tuples</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>list-operations</t>
+          <t>list-methods</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1677,17 +1750,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>lists</t>
+          <t>lists-and-tuples</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1821,10 +1904,510 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Python - Second Item</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Second Item. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Values
+### Output Format
+```
+2
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>lists</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1 2 3</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>5 9</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0 -1 2</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>10 20 30</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7 7 7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>100 200</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>-5 -4 -3</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>print(input().split()[1])</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Append Total</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Append Total. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Prices
+- Line 2: New price
+### Output Format
+```
+10
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>list-methods</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1 2 3
+4</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>10
+5</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0 0
+1</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5 5 5
+5</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>100 200
+50</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>-1 2
+3</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>7
+8</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>p=list(map(int,input().split())); p.append(int(input())); print(sum(p))</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>Python - Sort by Marks</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>After the internal exams, Professor Rao wants a merit list pinned on the notice board: student names arranged from the highest scorer down to the lowest. If two students score the same, whoever appeared first in the register stays first.
 Read `N`, then `N` lines each containing a student's name and score. Print only the names, one per line, ordered from highest score to lowest. Students with equal scores keep their original input order.
@@ -1844,54 +2427,64 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>lists</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>tuples</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>list-methods</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>3
 asha 80
@@ -1899,43 +2492,43 @@
 meera 70</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>kabir
 asha
 meera</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>1
 sam 50</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>sam</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>2
 a 10
 b 10</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>a
 b</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>4
 a 0
@@ -1944,7 +2537,7 @@
 d 50</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>b
 c
@@ -1952,20 +2545,20 @@
 a</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>2
 x -5
 y -10</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>x
 y</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>5
 p 60
@@ -1975,7 +2568,7 @@
 t 90</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>r
 t
@@ -1984,7 +2577,7 @@
 s</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>n = int(input())
 students = []
@@ -1997,13 +2590,13 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Adjacent Products</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Simran is setting a number puzzle for the class magazine. She writes a row of numbers and asks readers to build the next row by multiplying each pair of neighbours — the 1st number times the 2nd, the 2nd times the 3rd, and so on.
 Read a line of space-separated numbers and print the product of every adjacent (neighbouring) pair, in order, separated by spaces. A list of `N` numbers produces `N-1` products.
@@ -2020,124 +2613,134 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>lists</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>list-comprehensions</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>2 6 12</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>2 5</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>3 3 3</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>9 9</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>-1 -2 -3</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>2 6</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>1 1 1 1 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1 1 1 1</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2 6 12 20 30 42 56 72 90</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 products = [nums[i] * nums[i + 1] for i in range(len(nums) - 1)]
@@ -2145,13 +2748,13 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Cart Total</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>An online cart adds up the prices of the items in it. Read a line of space-separated prices and print their total.
 ### Input Format
@@ -2160,142 +2763,154 @@
 ```
 150
 ```
+### Example Walkthrough
+In the sample, the prices are `50 40 60`. Adding them gives `150`, so the program prints `150`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>list-operations</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O12" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P12" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="b">
-        <v>1</v>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>10 20 30 40 50</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>-1 -2 3</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0 0 0</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>-5 -10 -15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>-30</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>prices = list(map(int, input().split()))
 print(sum(prices))</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Item Count</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Read a line of space-separated values and print how many values there are.
 ### Input Format
@@ -2304,142 +2919,154 @@
 ```
 5
 ```
+### Example Walkthrough
+In the sample, the input is `a b c d e`. It has `5` values, so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>list-operations</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O13" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P13" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="b">
-        <v>1</v>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>3 1 4 1 5</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>7 8 9 10</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>x x x</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>a b c d e f g h i j k l m n o</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>items = input().split()
 print(len(items))</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Most Expensive</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Read a line of space-separated prices and print the largest one.
 ### Input Format
@@ -2448,142 +3075,154 @@
 ```
 55
 ```
+### Example Walkthrough
+In the sample, the prices are `20 55 30`. The largest is `55`, so the program prints `55`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>list-operations</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O14" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P14" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>1</v>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>10 55 30</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>-1 -9 -3</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>5 5 5</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>-100 100 0</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>prices = list(map(int, input().split()))
 print(max(prices))</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Cheapest</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Read a line of space-separated prices and print the smallest one.
 ### Input Format
@@ -2592,142 +3231,154 @@
 ```
 10
 ```
+### Example Walkthrough
+In the sample, the prices are `10 25 40`. The smallest is `10`, so the program prints `10`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>list-operations</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O15" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="b">
-        <v>1</v>
-      </c>
-      <c r="R15" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>10 55 30</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>-1 -9 -3</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>5 5 5</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>-100 100 0</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>-100</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>prices = list(map(int, input().split()))
 print(min(prices))</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - First Three</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>A leaderboard shows only the top three entries. Read a line of space-separated values and print the first three, separated by spaces (or all of them if there are fewer than three).
 ### Input Format
@@ -2736,142 +3387,154 @@
 ```
 1 2 3
 ```
+### Example Walkthrough
+In the sample, the input is `1 2 3 4 5`. The first three values are `1`, `2`, and `3`, so the program prints `1 2 3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>list-operations</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O16" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P16" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>1</v>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>9 8</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>9 8</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>a b c</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>a b c</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>a b c d e f g h</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>a b c</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>items = input().split()
 print(*items[:3])</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Python - Last Item</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Read a line of space-separated values and print the last one.
 ### Input Format
@@ -2880,142 +3543,654 @@
 ```
 cherry
 ```
+### Example Walkthrough
+In the sample, the input is `apple banana cherry`. The last value is `cherry`, so the program prints `cherry`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>list-operations</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O17" t="b">
+      <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P17" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="b">
-        <v>1</v>
-      </c>
-      <c r="R17" t="inlineStr">
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>apple banana cherry</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>cherry</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>solo</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>solo</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>x y</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>y</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>a b c d e f g h i j</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>j</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>items = input().split()
 print(items[-1])</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Tuple Swap</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Tuple Swap. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: x
+- Line 2: y
+### Output Format
+```
+2 1
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>tuples</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1
+2</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2 1</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>A
+B</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>B A</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>left
+right</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>right left</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0
+0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0 0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>hello
+world</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>world hello</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>5
+-1</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>-1 5</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>x
+y</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>y x</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>x=input(); y=input(); x,y=y,x; print(x,y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Sorted Copy</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Sorted Copy. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Integers
+### Output Format
+```
+1 2 3
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>list-methods</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3 1 2</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1 2 3</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0 -1 10</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-1 0 10</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>9 9 1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>1 9 9</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>100 50 75</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>50 75 100</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>-3 -5 -1</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>-5 -3 -1</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>8 6 7</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>6 7 8</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>print(*sorted(map(int,input().split())))</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Count a Value</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Read a line of space-separated values, then a value to look for, and print how many times it appears in the list.
 ### Input Format
@@ -3025,136 +4200,148 @@
 ```
 3
 ```
+### Example Walkthrough
+In the sample, the list is `a b a c a` and the target is `a`. It appears `3` times, so the program prints `3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>lists</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>list-operations</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>list-methods</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O18" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>1</v>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>1 2 2 3 2
 2</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>a b c
 z</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>5 5 5
 5</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>a
 a</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>1 1 1 1 1
 1</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>x y z
 x</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>a b a b a b a
 b</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>items = input().split()
 target = input()
@@ -3162,13 +4349,13 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Top Scores First</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Read a line of space-separated scores and print them sorted from highest to lowest, separated by spaces.
 ### Input Format
@@ -3177,142 +4364,154 @@
 ```
 5 4 3 1 1
 ```
+### Example Walkthrough
+In the sample, the scores are `3 1 4 1 5`. Sorted from highest to lowest they become `5, 4, 3, 1, 1`, so the program prints `5 4 3 1 1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>lists</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>list-operations</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>list-methods</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O19" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P19" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="b">
-        <v>1</v>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>3 1 4 1 5</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>5 4 3 1 1</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>10 20</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>20 10</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>-5 -1 -10</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>-1 -5 -10</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>5 5 5</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>5 5 5</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>9 3 7 1 8 2 6 4 0 5</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>9 8 7 6 5 4 3 2 1 0</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 print(*sorted(nums, reverse=True))</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Runner-Up Score</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Read a line of space-separated scores and print the second-highest distinct score.
 ### Input Format
@@ -3321,129 +4520,141 @@
 ```
 5
 ```
+### Example Walkthrough
+In the sample, the scores are `5 8 5 3`. The distinct scores in descending order are `8, 5, 3`, so the second-highest is `5`, and the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>lists</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>list-operations</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>list-methods</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O20" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P20" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="b">
-        <v>1</v>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>3 1 4 1 5 9</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>5 5 4</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>0 1</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>-1 -2 -3</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>10 10 9</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>100 90 80 70 60</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 distinct = sorted(set(nums), reverse=True)
@@ -3451,13 +4662,13 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Keep the Evens</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Read a line of space-separated numbers and print only the even ones, in the same order, separated by spaces. Use a list comprehension.
 ### Input Format
@@ -3466,124 +4677,136 @@
 ```
 2 4 6
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3 4 5 6`. The even ones, in order, are `2`, `4`, and `6`, so the program prints `2 4 6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>lists</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>list-comprehensions</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O21" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P21" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="b">
-        <v>1</v>
-      </c>
-      <c r="R21" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>2 4 6</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>2 3 4</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>2 4</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>10 15 20</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>10 20</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>1 3 5 7</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>-2 -4 -1</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>-2 -4</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2 4 6 8 10</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 evens = [x for x in nums if x % 2 == 0]
@@ -3591,13 +4814,13 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Even-Index Sum</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Read a line of space-separated numbers and print the sum of the values at the even positions 0, 2, 4, and so on.
 ### Input Format
@@ -3606,142 +4829,154 @@
 ```
 90
 ```
+### Example Walkthrough
+In the sample, the numbers are `10 5 20 5 60`. The values at positions `0`, `2`, and `4` are `10`, `20`, and `60`, which sum to `90`, so the program prints `90`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>list-operations</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O22" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P22" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>1</v>
-      </c>
-      <c r="R22" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>10 20 30 40 50</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>-1 -2 -3 -4 -5</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 print(sum(nums[::2]))</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Rotate Right by One</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Read a line of space-separated values and print them rotated one place to the right, so the last value moves to the front.
 ### Input Format
@@ -3750,129 +4985,141 @@
 ```
 4 1 2 3
 ```
+### Example Walkthrough
+In the sample, the input is `1 2 3 4`. Moving the last value to the front gives `4 1 2 3`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>list-operations</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O23" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P23" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="b">
-        <v>1</v>
-      </c>
-      <c r="R23" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>4 1 2 3</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>a b</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>b a</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>8 1 2 3 4 5 6 7</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>x y z</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>z x y</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>a b c d e f g h i j</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>j a b c d e f g h i</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>items = input().split()
 rotated = items[-1:] + items[:-1]
@@ -3880,13 +5127,13 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Position Finder</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Read a line of space-separated numbers, then a target. Print the 1-based position of the first time the target appears, or 0 if it does not appear.
 ### Input Format
@@ -3896,136 +5143,148 @@
 ```
 2
 ```
+### Example Walkthrough
+In the sample, the numbers are `5 3 8` and the target is `3`. It first appears at 1-based position `2`, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>lists</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>list-operations</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>list-methods</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O24" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P24" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>1</v>
-      </c>
-      <c r="R24" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>10 20 30
 20</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>1 2 3
 5</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>5 5 5
 5</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>-1 -2 -3
 -2</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>1 2 3 2 1
 2</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10
 10</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 target = int(input())
@@ -4036,15 +5295,684 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Even List</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Even List. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Integers
+### Output Format
+```
+2 4
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>list-comprehensions</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1 2 3 4</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2 4</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>5 7</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0 2 4</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0 2 4</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>-2 -1 3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10 11 12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>10 12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>8 8 9</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>8 8</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>nums=list(map(int,input().split())); print(*[x for x in nums if x%2==0])</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Nested Row Sums</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Nested Row Sums. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Rows
+- Next rows: Integers
+### Output Format
+```
+3
+7
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>nested-lists</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2
+1 2
+3 4</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3
+7</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1
+5 5</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3
+1
+2
+3</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>1
+2
+3</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2
+0 0
+1 1</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0
+2</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2
+-1 2
+3 -4</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1
+-1</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>1
+10 20 30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>3
+1 1
+2 2
+3 3</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2
+4
+6</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>r=int(input())
+for _ in range(r): print(sum(map(int,input().split())))</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Pair Products</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Pair Products. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: First list
+- Line 2: Second list
+### Output Format
+```
+4 10 18
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>sequence-iteration</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1 2 3
+4 5 6</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>4 10 18</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2
+3</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0 1
+5 6</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0 6</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-1 2
+3 -4</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>-3 -8</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10 20
+1 2</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>10 40</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>1 1 1
+9 8 7</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>9 8 7</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>5 6 7
+0 1 2</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>0 6 14</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>a=list(map(int,input().split())); b=list(map(int,input().split())); print(*[x*y for x,y in zip(a,b)])</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Column Sums</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Read a grid with R rows and C columns and print the sum of each column on one line, separated by spaces.
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Read a grid with `R` rows and `C` columns and print the sum of each column on one line, separated by spaces.
 ### Input Format
 - Line 1: R and C separated by a space
 - Next R lines: C space-separated numbers each
@@ -4052,82 +5980,94 @@
 ```
 5 7 9
 ```
+### Example Walkthrough
+In the sample, the grid is `2` rows by `3` columns: `1 2 3` and `4 5 6`. The column sums are `1 + 4 = 5`, `2 + 5 = 7`, and `3 + 6 = 9`, so the program prints `5 7 9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>lists</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>nested-lists</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O25" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P25" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="b">
-        <v>1</v>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>2 3
 1 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>5 7 9</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>1 1
 7</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>3 2
 1 1
@@ -4135,35 +6075,35 @@
 3 3</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>6 6</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>1 4
 1 2 3 4</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>2 2
 -1 -2
 -3 -4</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>-4 -6</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>4 1
 1
@@ -4172,12 +6112,12 @@
 4</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>3 3
 1 2 3
@@ -4185,12 +6125,12 @@
 7 8 9</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>12 15 18</t>
         </is>
       </c>
-      <c r="AG25" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>r, c = map(int, input().split())
 grid = [list(map(int, input().split())) for _ in range(r)]
@@ -4199,15 +6139,15 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Flatten the Rows</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Read R rows, each a line of space-separated numbers of any length, and print all the numbers on a single line, separated by spaces, in order.
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Read `R` rows, each a line of space-separated numbers of any length, and print all the numbers on a single line, separated by spaces, in order.
 ### Input Format
 - Line 1: R, the number of rows
 - Next R lines: space-separated numbers each
@@ -4215,82 +6155,94 @@
 ```
 1 2 3 4 5
 ```
+### Example Walkthrough
+In the sample, `R` is `2` with rows `1 2 3` and `4 5`. Combined in order, they form `1 2 3 4 5`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>lists</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>nested-lists</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O26" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P26" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="b">
-        <v>1</v>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>2
 1 2
 3 4 5</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>1
 9</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>3
 1
@@ -4298,28 +6250,28 @@
 3</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>1
 1 2 3 4 5 6 7</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>4
 1
@@ -4328,24 +6280,24 @@
 7</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>2
 1 2 3 4 5
 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>r = int(input())
 flat = []
@@ -4355,15 +6307,15 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Diagonal Sum</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Read a square grid of size N and print the sum of the values on its main diagonal (top-left to bottom-right).
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Read a square grid of size `N` and print the sum of the values on its main diagonal (top-left to bottom-right).
 ### Input Format
 - Line 1: N
 - Next N lines: N space-separated numbers each
@@ -4371,59 +6323,71 @@
 ```
 15
 ```
+### Example Walkthrough
+In the sample, `N` is `3` with rows `1 2 3`, `4 5 6`, and `7 8 9`. The diagonal values are `1`, `5`, and `9`, which sum to `15`, so the program prints `15`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>lists</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>nested-lists</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O27" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="b">
-        <v>1</v>
-      </c>
-      <c r="R27" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>3
 1 2 3
@@ -4431,46 +6395,46 @@
 7 8 9</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>1
 5</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>2
 1 2
 3 4</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>1
 0</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>4
 1 0 0 0
@@ -4479,24 +6443,24 @@
 0 0 0 4</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>2
 -1 -2
 -3 -4</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>5
 1 2 3 4 5
@@ -4506,12 +6470,12 @@
 21 22 23 24 25</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>n = int(input())
 grid = [list(map(int, input().split())) for _ in range(n)]
@@ -4520,15 +6484,15 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Row Maximums</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Read a grid with R rows and C columns and print the largest value in each row, one per line, top to bottom.
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Read a grid with `R` rows and `C` columns and print the largest value in each row, one per line, top to bottom.
 ### Input Format
 - Line 1: R and C separated by a space
 - Next R lines: C space-separated numbers each
@@ -4537,107 +6501,119 @@
 9
 8
 ```
+### Example Walkthrough
+In the sample, the grid is `2` rows by `3` columns: `3 9 5` and `8 2 1`. The largest value in the first row is `9` and in the second row is `8`, so the program prints `9` then `8`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>lists</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>nested-lists</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O28" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P28" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="b">
-        <v>1</v>
-      </c>
-      <c r="R28" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>2 3
 1 9 3
 4 2 8</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>9
 8</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>1 1
 7</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>2 2
 -1 -2
 -3 -4</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>-1
 -3</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>1 4
 1 2 3 4</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>3 1
 5
@@ -4645,27 +6621,27 @@
 8</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>5
 2
 8</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>2 2
 0 0
 0 0</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>4 3
 1 2 3
@@ -4674,7 +6650,7 @@
 10 11 12</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>3
 6
@@ -4682,7 +6658,7 @@
 12</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>r, c = map(int, input().split())
 for _ in range(r):
@@ -4691,13 +6667,13 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Value Counts</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Read a line of space-separated numbers and, for each distinct value in ascending order, print the value and how many times it appears in the form 'value:count', one per line.
 ### Input Format
@@ -4708,129 +6684,141 @@
 2:2
 3:3
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 2 3 3 3`. The distinct values in ascending order are `1`, `2`, and `3`, appearing `1`, `2`, and `3` times respectively, so the program prints `1:1`, `2:2`, and `3:3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>lists</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>list-operations</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>list-methods</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O29" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="b">
-        <v>1</v>
-      </c>
-      <c r="R29" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>1 2 2 3 3 3</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>1:1
 2:2
 3:3</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>5 5</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>5:2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>3 1 2</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>1:1
 2:1
 3:1</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>-1 -1 -2</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>-2:1
 -1:2</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>7 7 7 7 7</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>7:5</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1:1
 2:1
@@ -4844,7 +6832,7 @@
 10:1</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 for v in sorted(set(nums)):
@@ -4852,13 +6840,13 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Two-Sum Positions</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Read a line of space-separated numbers and a target. Print the 1-based positions of the first pair of values (earlier position first) that add up to the target, separated by a space. Print 'None' if there is no such pair.
 ### Input Format
@@ -4868,136 +6856,148 @@
 ```
 1 2
 ```
+### Example Walkthrough
+In the sample, the numbers are `2 7 11 15` and the target is `9`. The first pair that adds up to `9` is `2` and `7`, at 1-based positions `1` and `2`, so the program prints `1 2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>nested-lists</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O30" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P30" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R30" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>2 7 11 15
 9</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>1 2 3
 7</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3 3
 6</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>0 0
 0</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>-1 -2 -3
 -5</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>2 3</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>5 5 5 5
 10</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10
 19</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>9 10</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 target = int(input())
@@ -5013,13 +7013,13 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Common Elements</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Read two lines of space-separated values. Print the values that appear in both lists, in the order they appear in the first list, separated by spaces (each common value once).
 ### Input Format
@@ -5029,131 +7029,143 @@
 ```
 2 4
 ```
+### Example Walkthrough
+In the sample, the lists are `1 2 3 4` and `2 4 6`. The values `2` and `4` appear in both, in the order they appear in the first list, so the program prints `2 4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>list-operations</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O31" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="b">
-        <v>1</v>
-      </c>
-      <c r="R31" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>1 2 3 4
 2 4 6</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>2 4</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>5 6 7
 6 7 8</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>6 7</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>1 2
 2 1</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>a
 a</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>1 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>x x y y
 y x</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>x y</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10
 2 4 6 8 10 12</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2 4 6 8 10</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>a = input().split()
 b = input().split()
@@ -5165,6 +7177,515 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Rotate Left</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Rotate Left. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Values
+- Line 2: K
+### Output Format
+```
+b c d a
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>list-methods</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>a b c d
+1</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>b c d a</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1 2 3
+2</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3 1 2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>x
+5</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>p q r
+0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>p q r</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>1 2 3 4 5
+7</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>3 4 5 1 2</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>A B
+3</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>B A</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>red blue green
+2</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>green red blue</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>items=input().split(); k=int(input())%len(items); print(*(items[k:]+items[:k]))</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Matrix Diagonal</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Matrix Diagonal. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+- Next N lines: Row
+### Output Format
+```
+5
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>nested-lists</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2
+1 2
+3 4</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1
+5</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3
+1 0 0
+0 2 0
+0 0 3</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2
+-1 2
+3 -4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3
+1 2 3
+4 5 6
+7 8 9</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>4
+1 0 0 0
+0 1 0 0
+0 0 1 0
+0 0 0 1</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2
+0 0
+0 0</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>n=int(input()); total=0
+for i in range(n): total+=list(map(int,input().split()))[i]
+print(total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Tuple Grade Sort</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Tuple Grade Sort. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+- Next N lines: name score
+### Output Format
+```
+Meena Asha Rohan
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>lists-and-tuples</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>tuples</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3
+Asha 90
+Rohan 80
+Meena 95</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Meena Asha Rohan</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1
+A 10</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2
+X 5
+Y 5</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>X Y</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3
+A 1
+B 3
+C 2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>B C A</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2
+Dev 100
+Zoya 99</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Dev Zoya</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>4
+a 4
+b 1
+c 3
+d 2</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>a c d b</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2
+Low -1
+High 0</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>High Low</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>n=int(input()); rec=[]
+for _ in range(n):
+ name,score=input().split(); rec.append((name,int(score)))
+rec.sort(key=lambda x:x[1], reverse=True)
+print(*[x[0] for x in rec])</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/Question Bank/Coding Questions/Unit 6 - Lists and Tuples/Unit 6 - Lists and Tuples - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 6 - Lists and Tuples/Unit 6 - Lists and Tuples - Coding Questions.xlsx
@@ -1909,16 +1909,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Second Item. Read the input values and print the required result exactly.
+          <t>During the school sports day, the announcer lists the finishing order of runners in a race as space-separated bib numbers. The organizers want to quickly identify the runner who finished in second place.
+Read one line of space-separated values. Print the second value in the list (the value at index 1, using 0-based indexing) exactly as it appears in the input.
 ### Input Format
-- Line 1: Values
+- Line 1: Space-separated values
 ### Output Format
 ```
 2
 ```
+### Example Walkthrough
+The sample input is `1 2 3`. The values in order are 1, 2, 3. The second value is 2, so the program prints `2`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The list contains at least two values.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2062,17 +2065,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Append Total. Read the input values and print the required result exactly.
+          <t>A shopkeeper maintains a running list of item prices already placed in a customer's cart. The customer then adds one more item at checkout, and the shopkeeper needs the new total bill immediately.
+Read a line of space-separated integers representing the existing prices, then read one more line containing a single integer for the new item's price. Append this new price to the list and print the sum of all the prices (the original prices plus the new one).
 ### Input Format
-- Line 1: Prices
-- Line 2: New price
+- Line 1: Space-separated integers (existing prices)
+- Line 2: A single integer (new price to append)
 ### Output Format
 ```
 10
 ```
+### Example Walkthrough
+The existing prices are `1 2 3` and the new price is `4`. Appending 4 gives the list [1, 2, 3, 4], whose sum is 1+2+3+4=10, so the program prints `10`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid integers in the ranges implied by the examples.
+- The new price must be appended to the list before computing the total.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3692,17 +3698,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Tuple Swap. Read the input values and print the required result exactly.
+          <t>A stage manager tracks the order of two performers, x and y, who take turns opening the show. Just before curtain call, the manager swaps their order for the closing act.
+Read two values x and y, one per line. Swap their positions using tuple assignment and print the swapped values separated by a single space (the value originally read as y first, then the value originally read as x).
 ### Input Format
-- Line 1: x
-- Line 2: y
+- Line 1: Value x
+- Line 2: Value y
 ### Output Format
 ```
 2 1
 ```
+### Example Walkthrough
+x is `1` and y is `2`. After swapping, x becomes 2 and y becomes 1, so the program prints `2 1`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- Inputs may be numbers or text and are printed back exactly as read (as strings).
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -3853,16 +3862,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Sorted Copy. Read the input values and print the required result exactly.
+          <t>A librarian receives a shelf's book ID numbers in random order as items are returned. To restock efficiently, she needs a sorted copy of the list from smallest to largest ID, separate from the original order noted by the front desk.
+Read one line of space-separated integers. Create a new sorted copy of these integers in ascending order and print them separated by single spaces.
 ### Input Format
-- Line 1: Integers
+- Line 1: Space-separated integers
 ### Output Format
 ```
 1 2 3
 ```
+### Example Walkthrough
+The sample input is `3 1 2`. Sorting these integers in ascending order gives 1, 2, 3, so the program prints `1 2 3`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid integers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -5303,16 +5315,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Even List. Read the input values and print the required result exactly.
+          <t>At a raffle draw, the host reads out a list of ticket numbers collected in a box. Only tickets with even numbers qualify for the bonus prize round.
+Read one line of space-separated integers. Keep only the even numbers (numbers exactly divisible by 2, including 0) and print them in their original order, separated by single spaces. If no even numbers are present, print a blank line.
 ### Input Format
-- Line 1: Integers
+- Line 1: Space-separated integers
 ### Output Format
 ```
 2 4
 ```
+### Example Walkthrough
+The sample input is `1 2 3 4`. Checking each number for divisibility by 2: 1 is odd, 2 is even, 3 is odd, 4 is even. The even numbers in order are 2 and 4, so the program prints `2 4`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid integers in the ranges implied by the examples.
+- If the list contains no even numbers, the program prints an empty line.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -5387,7 +5402,6 @@
           <t>5 7</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>0 2 4</t>
@@ -5423,7 +5437,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
           <t>8 8 9</t>
@@ -5448,18 +5461,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Nested Row Sums. Read the input values and print the required result exactly.
+          <t>A teacher records marks scored by each student across several subjects, one row per student, and wants each student's total marks printed on its own line.
+Read an integer R (the number of rows). Then read R more lines, each containing space-separated integers. For each of these R lines, compute the sum of the integers on that line and print it on its own line, in the same order the rows were read.
 ### Input Format
-- Line 1: Rows
-- Next rows: Integers
+- Line 1: An integer R, the number of rows
+- Next R lines: Space-separated integers for that row
 ### Output Format
 ```
 3
 7
 ```
+### Example Walkthrough
+R is `2`. The first row is `1 2`, whose sum is 3. The second row is `3 4`, whose sum is 7. The program prints each row's sum on its own line: `3` then `7`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid integers in the ranges implied by the examples.
+- Each row's sum must be printed on its own line, in the same order the rows were read.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -5625,17 +5641,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Pair Products. Read the input values and print the required result exactly.
+          <t>A store manager keeps two lists for a sale: the quantity of each item sold and the price per unit of each item, listed in matching order. She needs the revenue generated by each item.
+Read two lines of space-separated integers, list A and list B. Pair up the elements at the same position from each list (the first element of A with the first of B, the second with the second, and so on) and print the product of each pair, separated by single spaces. If the lists are of different lengths, only pair up to the length of the shorter list.
 ### Input Format
-- Line 1: First list
-- Line 2: Second list
+- Line 1: Space-separated integers (list A)
+- Line 2: Space-separated integers (list B)
 ### Output Format
 ```
 4 10 18
 ```
+### Example Walkthrough
+List A is `1 2 3` and list B is `4 5 6`. Multiplying elements at matching positions: 1x4=4, 2x5=10, 3x6=18, so the program prints `4 10 18`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid integers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -7185,17 +7204,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Rotate Left. Read the input values and print the required result exactly.
+          <t>In a relay race, four runners line up in a fixed order. After each lap, the team rotates its running order to the left by a certain number of positions so a different runner starts the next lap.
+Read a line of space-separated items, then an integer K on the next line. Rotate the list to the left by K positions - that is, move the first K items to the end of the list, preserving the relative order of all items - and print the resulting list separated by single spaces. If K is larger than the number of items, use K modulo the number of items as the effective rotation amount.
 ### Input Format
-- Line 1: Values
-- Line 2: K
+- Line 1: Space-separated items
+- Line 2: An integer K, the number of positions to rotate left
 ### Output Format
 ```
 b c d a
 ```
+### Example Walkthrough
+The items are `a b c d` and K is `1`. Rotating left by 1 position moves `a` from the front to the back, giving `b c d a`, so the program prints `b c d a`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The list contains at least one item.
+- K may be 0 or larger than the number of items, in which case the rotation wraps around (K modulo the list length is used).</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -7346,17 +7368,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Matrix Diagonal. Read the input values and print the required result exactly.
+          <t>A game designer stores a square grid of tile values for a puzzle level. To check the puzzle's balance, she needs the sum of the values that lie along the main diagonal, running from the top-left corner to the bottom-right corner.
+Read an integer N (the size of a square matrix), then read N lines each containing N space-separated integers, forming the matrix. Compute the sum of the diagonal elements - the element at row i, column i, for each row i from 0 to N-1 - and print the total.
 ### Input Format
-- Line 1: N
-- Next N lines: Row
+- Line 1: An integer N, the size of the square matrix
+- Next N lines: N space-separated integers each, forming one row of the matrix
 ### Output Format
 ```
 5
 ```
+### Example Walkthrough
+N is `2`. The matrix rows are `1 2` and `3 4`. The diagonal elements are the value at row 0, column 0 (which is 1) and the value at row 1, column 1 (which is 4). Their sum is 1+4=5, so the program prints `5`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- N is a positive integer, and each row contains exactly N integers.
+- Only the main diagonal (row index equal to column index) is summed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -7519,17 +7544,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Tuple Grade Sort. Read the input values and print the required result exactly.
+          <t>A teacher records each student's name along with their exam score, entered as pairs. Before announcing results, she wants the names listed in order from the highest scorer to the lowest.
+Read an integer N (the number of students), then read N lines each containing a student's name and score separated by a space. Sort the students by score in descending order (highest score first). If two students have the same score, keep them in the order they were originally entered (a stable sort). Print only the names, in the sorted order, separated by single spaces.
 ### Input Format
-- Line 1: N
-- Next N lines: name score
+- Line 1: An integer N, the number of students
+- Next N lines: A name and a score, space-separated
 ### Output Format
 ```
 Meena Asha Rohan
 ```
+### Example Walkthrough
+N is `3`. The students are Asha with 90, Rohan with 80, and Meena with 95. Sorting by score from highest to lowest gives Meena (95), Asha (90), Rohan (80), so the program prints `Meena Asha Rohan`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- Scores are valid integers, and ties are broken by keeping the original input order (stable sort).
+- Every name must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">

--- a/content/Question Bank/Coding Questions/Unit 6 - Lists and Tuples/Unit 6 - Lists and Tuples - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 6 - Lists and Tuples/Unit 6 - Lists and Tuples - Coding Questions.xlsx
@@ -1909,8 +1909,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>During the school sports day, the announcer lists the finishing order of runners in a race as space-separated bib numbers. The organizers want to quickly identify the runner who finished in second place.
-Read one line of space-separated values. Print the second value in the list (the value at index 1, using 0-based indexing) exactly as it appears in the input.
+          <t>A relay race results board records the finish order of runners as space-separated bib numbers on one line, and the announcer needs to quickly call out just the second-place runner's bib number.
+Write a program that reads a line of space-separated values and prints only the second value (the one at index 1).
 ### Input Format
 - Line 1: Space-separated values
 ### Output Format
@@ -1918,9 +1918,9 @@
 2
 ```
 ### Example Walkthrough
-The sample input is `1 2 3`. The values in order are 1, 2, 3. The second value is 2, so the program prints `2`.
+In the sample, the line is `1 2 3`. Splitting it into a list gives `['1', '2', '3']`, and the second value (index 1) is `2`, which the program prints.
 ### Constraints
-- The list contains at least two values.
+- The input line has at least two space-separated values.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -2065,20 +2065,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A shopkeeper maintains a running list of item prices already placed in a customer's cart. The customer then adds one more item at checkout, and the shopkeeper needs the new total bill immediately.
-Read a line of space-separated integers representing the existing prices, then read one more line containing a single integer for the new item's price. Append this new price to the list and print the sum of all the prices (the original prices plus the new one).
+          <t>A shopping cart already holds a few item prices, and at checkout the cashier types in the price of one more item; the till needs the grand total including that last item.
+Write a program that reads a line of space-separated numbers into a list, reads one more number on the next line and appends it to the list, then prints the sum of the whole list.
 ### Input Format
-- Line 1: Space-separated integers (existing prices)
-- Line 2: A single integer (new price to append)
+- Line 1: Space-separated numbers (the existing cart)
+- Line 2: One more number (the item added at checkout)
 ### Output Format
 ```
 10
 ```
 ### Example Walkthrough
-The existing prices are `1 2 3` and the new price is `4`. Appending 4 gives the list [1, 2, 3, 4], whose sum is 1+2+3+4=10, so the program prints `10`.
+In the sample, the cart is `1 2 3` and the new item costs `4`. Appending 4 to the list gives `[1, 2, 3, 4]`, and summing it gives 10, so the program prints `10`.
 ### Constraints
-- All numeric inputs are valid integers in the ranges implied by the examples.
-- The new price must be appended to the list before computing the total.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3698,19 +3698,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A stage manager tracks the order of two performers, x and y, who take turns opening the show. Just before curtain call, the manager swaps their order for the closing act.
-Read two values x and y, one per line. Swap their positions using tuple assignment and print the swapped values separated by a single space (the value originally read as y first, then the value originally read as x).
+          <t>A seating app swaps the assigned seats of two passengers the moment they request an exchange, so passenger A gets passenger B's seat and vice versa.
+Write a program that reads two values on separate lines, swaps them, and prints the swapped values separated by a single space (second value first, then the first value).
 ### Input Format
-- Line 1: Value x
-- Line 2: Value y
+- Line 1: First value
+- Line 2: Second value
 ### Output Format
 ```
 2 1
 ```
 ### Example Walkthrough
-x is `1` and y is `2`. After swapping, x becomes 2 and y becomes 1, so the program prints `2 1`.
+In the sample, the values are `1` and `2`. After swapping, the first holder now has `2` and the second holder has `1`, so the program prints `2 1`.
 ### Constraints
-- Inputs may be numbers or text and are printed back exactly as read (as strings).
+- The inputs are valid values with no leading or trailing spaces.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -3862,18 +3862,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A librarian receives a shelf's book ID numbers in random order as items are returned. To restock efficiently, she needs a sorted copy of the list from smallest to largest ID, separate from the original order noted by the front desk.
-Read one line of space-separated integers. Create a new sorted copy of these integers in ascending order and print them separated by single spaces.
+          <t>A photo-gallery app arranges uploaded photo IDs (given as space-separated numbers) in ascending order before displaying the thumbnail grid, so viewers always see photos in a predictable order.
+Write a program that reads a line of space-separated whole numbers and prints them sorted from smallest to largest, separated by single spaces.
 ### Input Format
-- Line 1: Space-separated integers
+- Line 1: Space-separated whole numbers
 ### Output Format
 ```
 1 2 3
 ```
 ### Example Walkthrough
-The sample input is `3 1 2`. Sorting these integers in ascending order gives 1, 2, 3, so the program prints `1 2 3`.
+In the sample, the numbers are `3 1 2`. Sorted from smallest to largest they become 1, 2, 3, so the program prints `1 2 3`.
 ### Constraints
-- All numeric inputs are valid integers in the ranges implied by the examples.
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -5315,19 +5315,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>At a raffle draw, the host reads out a list of ticket numbers collected in a box. Only tickets with even numbers qualify for the bonus prize round.
-Read one line of space-separated integers. Keep only the even numbers (numbers exactly divisible by 2, including 0) and print them in their original order, separated by single spaces. If no even numbers are present, print a blank line.
+          <t>A raffle organizer wants to filter a submitted list of ticket numbers down to just the even-numbered tickets, since only even tickets qualify for the bonus draw.
+Write a program that reads a line of space-separated whole numbers and prints only the even ones, in their original order, separated by single spaces. If none are even, print an empty line.
 ### Input Format
-- Line 1: Space-separated integers
+- Line 1: Space-separated whole numbers
 ### Output Format
 ```
 2 4
 ```
 ### Example Walkthrough
-The sample input is `1 2 3 4`. Checking each number for divisibility by 2: 1 is odd, 2 is even, 3 is odd, 4 is even. The even numbers in order are 2 and 4, so the program prints `2 4`.
+In the sample, the numbers are `1 2 3 4`. Checking each one, 2 and 4 are even while 1 and 3 are not, so the program prints `2 4`.
 ### Constraints
-- All numeric inputs are valid integers in the ranges implied by the examples.
-- If the list contains no even numbers, the program prints an empty line.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -5461,21 +5461,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A teacher records marks scored by each student across several subjects, one row per student, and wants each student's total marks printed on its own line.
-Read an integer R (the number of rows). Then read R more lines, each containing space-separated integers. For each of these R lines, compute the sum of the integers on that line and print it on its own line, in the same order the rows were read.
+          <t>A spreadsheet-style grade sheet stores each student's row of assignment scores on its own line, and the teacher wants the row total printed for every student, one total per line, in the order they appear.
+Write a program that reads a whole number R (the number of students), then reads R lines each containing space-separated scores, and prints the sum of each row's scores on its own line.
 ### Input Format
-- Line 1: An integer R, the number of rows
-- Next R lines: Space-separated integers for that row
+- Line 1: R, the number of rows
+- Next R lines: space-separated numbers for that row
 ### Output Format
 ```
 3
 7
 ```
 ### Example Walkthrough
-R is `2`. The first row is `1 2`, whose sum is 3. The second row is `3 4`, whose sum is 7. The program prints each row's sum on its own line: `3` then `7`.
+In the sample, R is 2, the first row is `1 2` (sum 3) and the second row is `3 4` (sum 7), so the program prints `3` then `7`.
 ### Constraints
-- All numeric inputs are valid integers in the ranges implied by the examples.
-- Each row's sum must be printed on its own line, in the same order the rows were read.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -5641,19 +5641,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A store manager keeps two lists for a sale: the quantity of each item sold and the price per unit of each item, listed in matching order. She needs the revenue generated by each item.
-Read two lines of space-separated integers, list A and list B. Pair up the elements at the same position from each list (the first element of A with the first of B, the second with the second, and so on) and print the product of each pair, separated by single spaces. If the lists are of different lengths, only pair up to the length of the shorter list.
+          <t>An invoice calculator works out the amount for every line item by multiplying each item's quantity by its unit price, given as two parallel lists: quantities on the first line and prices on the second.
+Write a program that reads two lines of space-separated whole numbers of equal length, multiplies each pair of values at the same position together, and prints the results separated by single spaces.
 ### Input Format
-- Line 1: Space-separated integers (list A)
-- Line 2: Space-separated integers (list B)
+- Line 1: Space-separated quantities
+- Line 2: Space-separated prices (same count as quantities)
 ### Output Format
 ```
 4 10 18
 ```
 ### Example Walkthrough
-List A is `1 2 3` and list B is `4 5 6`. Multiplying elements at matching positions: 1x4=4, 2x5=10, 3x6=18, so the program prints `4 10 18`.
+In the sample, the quantities are `1 2 3` and the prices are `4 5 6`. Multiplying each pair gives 1x4=4, 2x5=10, and 3x6=18, so the program prints `4 10 18`.
 ### Constraints
-- All numeric inputs are valid integers in the ranges implied by the examples.
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -7204,20 +7204,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>In a relay race, four runners line up in a fixed order. After each lap, the team rotates its running order to the left by a certain number of positions so a different runner starts the next lap.
-Read a line of space-separated items, then an integer K on the next line. Rotate the list to the left by K positions - that is, move the first K items to the end of the list, preserving the relative order of all items - and print the resulting list separated by single spaces. If K is larger than the number of items, use K modulo the number of items as the effective rotation amount.
+          <t>A round-robin duty scheduler rotates a list of employee names to the left by however many days have passed, so a different person starts the queue each day, wrapping back to the beginning once everyone has had a turn.
+Write a program that reads a line of space-separated names, reads a whole number K on the next line, and prints the list rotated left by K positions (using K modulo the number of names, so rotating past the end wraps around).
 ### Input Format
-- Line 1: Space-separated items
-- Line 2: An integer K, the number of positions to rotate left
+- Line 1: Space-separated names
+- Line 2: K, the number of positions to rotate left
 ### Output Format
 ```
 b c d a
 ```
 ### Example Walkthrough
-The items are `a b c d` and K is `1`. Rotating left by 1 position moves `a` from the front to the back, giving `b c d a`, so the program prints `b c d a`.
+In the sample, the names are `a b c d` and K is 1. Rotating left by 1 moves `a` to the end, giving `b c d a`, which the program prints.
 ### Constraints
-- The list contains at least one item.
-- K may be 0 or larger than the number of items, in which case the rotation wraps around (K modulo the list length is used).</t>
+- The input names contain no spaces within a single name.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -7368,20 +7368,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A game designer stores a square grid of tile values for a puzzle level. To check the puzzle's balance, she needs the sum of the values that lie along the main diagonal, running from the top-left corner to the bottom-right corner.
-Read an integer N (the size of a square matrix), then read N lines each containing N space-separated integers, forming the matrix. Compute the sum of the diagonal elements - the element at row i, column i, for each row i from 0 to N-1 - and print the total.
+          <t>A venue's seating chart is laid out as a square grid of seat numbers, and the manager wants to know the total of just the diagonal seats (row 1 seat 1, row 2 seat 2, and so on) reserved for VIP placement.
+Write a program that reads a whole number N, then reads N lines each with N space-separated numbers forming a square grid, and prints the sum of the diagonal values (the value at row `i`, column `i`, for each row).
 ### Input Format
-- Line 1: An integer N, the size of the square matrix
-- Next N lines: N space-separated integers each, forming one row of the matrix
+- Line 1: N, the size of the grid
+- Next N lines: N space-separated numbers each
 ### Output Format
 ```
 5
 ```
 ### Example Walkthrough
-N is `2`. The matrix rows are `1 2` and `3 4`. The diagonal elements are the value at row 0, column 0 (which is 1) and the value at row 1, column 1 (which is 4). Their sum is 1+4=5, so the program prints `5`.
+In the sample, N is 2 and the grid is `1 2` then `3 4`. The diagonal values are the first row's first value (1) and the second row's second value (4), which sum to 5, so the program prints `5`.
 ### Constraints
-- N is a positive integer, and each row contains exactly N integers.
-- Only the main diagonal (row index equal to column index) is summed.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -7544,20 +7544,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A teacher records each student's name along with their exam score, entered as pairs. Before announcing results, she wants the names listed in order from the highest scorer to the lowest.
-Read an integer N (the number of students), then read N lines each containing a student's name and score separated by a space. Sort the students by score in descending order (highest score first). If two students have the same score, keep them in the order they were originally entered (a stable sort). Print only the names, in the sorted order, separated by single spaces.
+          <t>A sports day results board lists each participant's name and score as they are submitted, and needs to display the final ranking from highest score to lowest, keeping the original entry order when two participants tie.
+Write a program that reads a whole number N, then reads N lines each with a name and a score separated by a space, and prints just the names in order from highest score to lowest, separated by single spaces.
 ### Input Format
-- Line 1: An integer N, the number of students
-- Next N lines: A name and a score, space-separated
+- Line 1: N, the number of participants
+- Next N lines: name and score separated by a space
 ### Output Format
 ```
 Meena Asha Rohan
 ```
 ### Example Walkthrough
-N is `3`. The students are Asha with 90, Rohan with 80, and Meena with 95. Sorting by score from highest to lowest gives Meena (95), Asha (90), Rohan (80), so the program prints `Meena Asha Rohan`.
+In the sample, N is 3 with Asha scoring 90, Rohan scoring 80, and Meena scoring 95. Ranking from highest to lowest score gives Meena (95), Asha (90), Rohan (80), so the program prints `Meena Asha Rohan`.
 ### Constraints
-- Scores are valid integers, and ties are broken by keeping the original input order (stable sort).
-- Every name must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Names contain no spaces, and scores are valid whole numbers.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">

--- a/content/Question Bank/Coding Questions/Unit 6 - Lists and Tuples/Unit 6 - Lists and Tuples - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 6 - Lists and Tuples/Unit 6 - Lists and Tuples - Coding Questions.xlsx
@@ -7,10 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - Coding - Unit 6" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH11"/>
+  <dimension ref="A1:AH41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,17 +598,11 @@
         <is>
           <t>At cricket practice, Coach Iyer jots down the runs his opening batsman scored in each recent match. Before the team meeting he wants the scores arranged from smallest to largest, so the batsman's best and worst days are easy to see.
 Read one line of space-separated numbers and print the same numbers sorted from smallest to largest, separated by single spaces.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-1 1 3 4 5
-```
 ### Example Walkthrough
 The sample scores are `3 1 4 1 5`. Arranged from smallest to largest they become 1, 1, 3, 4, 5, so the program prints `1 1 3 4 5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -743,8 +734,8 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>nums = list(map(int, input().split()))
-print(*sorted(nums))</t>
+          <t>nums = list(map(int, input().split()))   # read numbers from one line into a list
+print(*sorted(nums))   # sort ascending and print space-separated</t>
         </is>
       </c>
     </row>
@@ -758,18 +749,11 @@
         <is>
           <t>The juice stall outside the college gate writes today's available fruits on a small board. Customers keep asking, "Bhaiya, is banana there today?" — so the owner's son wants a program that answers instantly.
 Read a line of space-separated values (the list), then a single value on the next line. Print `Yes` if the value appears anywhere in the list, otherwise print `No`.
-### Input Format
-- Line 1: Space-separated values
-- Line 2: The value to search for
-### Output Format
-```
-Yes
-```
 ### Example Walkthrough
 The sample list is `apple banana cherry` and the value to find is `banana`. Since `banana` is in the list, the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -908,9 +892,9 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>items = input().split()
-target = input()
-print("Yes" if target in items else "No")</t>
+          <t>items = input().split()   # split the line into a list of strings
+target = input()   # value to search for
+print("Yes" if target in items else "No")   # membership check with 'in'</t>
         </is>
       </c>
     </row>
@@ -924,17 +908,11 @@
         <is>
           <t>Ravi takes the city bus to college every morning, and the bus stops at the same places in a fixed order. On the return trip in the evening, the bus visits exactly the same stops but backwards, and Ravi wants a program that prints the return-trip order.
 Read a line of space-separated values and print them in reverse order — last one first, first one last — separated by single spaces.
-### Input Format
-- Line 1: Space-separated values
-### Output Format
-```
-4 3 2 1
-```
 ### Example Walkthrough
 The sample input is `1 2 3 4`. Reversing the order puts 4 first and 1 last, so the program prints `4 3 2 1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1067,7 +1045,7 @@
       <c r="AG4" t="inlineStr">
         <is>
           <t>items = input().split()
-print(*items[::-1])</t>
+print(*items[::-1])   # slice with step -1 to reverse the list</t>
         </is>
       </c>
     </row>
@@ -1081,17 +1059,11 @@
         <is>
           <t>At the tech fest registration desk, excited students sometimes sign up two or three times for the same event. Organiser Sneha wants a clean participant list where each entry appears only once, kept in the order people first registered.
 Read a line of space-separated values and print each distinct value exactly once — that is, with all repeats removed — keeping the order in which each value first appeared, separated by spaces.
-### Input Format
-- Line 1: Space-separated values
-### Output Format
-```
-a b c
-```
 ### Example Walkthrough
 The sample input is `a b a c b a`. Reading left to right, `a` appears first, then `b`, then `c`; every later repeat of `a` or `b` is skipped, so the program prints `a b c`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1224,9 +1196,9 @@
       <c r="AG5" t="inlineStr">
         <is>
           <t>items = input().split()
-seen = []
+seen = []   # keeps unique values in first-seen order
 for x in items:
-    if x not in seen:
+    if x not in seen:   # skip values already added
         seen.append(x)
 print(*seen)</t>
         </is>
@@ -1242,17 +1214,11 @@
         <is>
           <t>Nisha is making flashcards of square numbers to help her younger brother prepare for his maths olympiad. For each number on a card, the back of the card must show that number multiplied by itself.
 Read a line of space-separated numbers and print the square of each number (the number multiplied by itself), in the same order, separated by spaces. Build the squared list using a list comprehension.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-1 4 9
-```
 ### Example Walkthrough
 The sample numbers are `1 2 3`. Squaring each gives 1×1 = 1, 2×2 = 4 and 3×3 = 9, so the program prints `1 4 9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1385,7 +1351,7 @@
       <c r="AG6" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-squares = [x * x for x in nums]
+squares = [x * x for x in nums]   # list comprehension: square every element
 print(*squares)</t>
         </is>
       </c>
@@ -1400,17 +1366,11 @@
         <is>
           <t>The hostel warden notes the electricity units consumed by the boys' hostel each day for a week. For his monthly report he only needs the two extremes — the lowest and the highest daily reading — written together as a pair.
 Read a line of space-separated numbers, find the smallest and the largest, and print them as a pair in the exact form `(min, max)` — with parentheses, a comma, and a space after the comma.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-(1, 5)
-```
 ### Example Walkthrough
 In the sample readings `3 1 4 1 5`, the smallest value is 1 and the largest is 5. Printed as a pair, that is `(1, 5)`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1543,8 +1503,8 @@
       <c r="AG7" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-pair = (min(nums), max(nums))
-print(f"({pair[0]}, {pair[1]})")</t>
+pair = (min(nums), max(nums))   # pack smallest and largest into a tuple
+print(f"({pair[0]}, {pair[1]})")   # format as (min, max)</t>
         </is>
       </c>
     </row>
@@ -1558,18 +1518,11 @@
         <is>
           <t>At the college fest, two ticket counters each kept their own list of token numbers sold during the day. At closing time, the accounts team needs all the tokens from both counters combined into one single list, arranged from smallest to largest.
 Read two lines, each containing space-separated numbers. Join the two groups into one list, sort it from smallest to largest, and print the numbers separated by spaces.
-### Input Format
-- Line 1: First group of space-separated numbers
-- Line 2: Second group of space-separated numbers
-### Output Format
-```
-1 2 3 4
-```
 ### Example Walkthrough
 The sample groups are `3 1` and `4 2`. Combined they form 3, 1, 4, 2, and sorting from smallest to largest gives `1 2 3 4`, which is what the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1710,7 +1663,7 @@
         <is>
           <t>a = list(map(int, input().split()))
 b = list(map(int, input().split()))
-print(*sorted(a + b))</t>
+print(*sorted(a + b))   # concatenate both lists, then sort ascending</t>
         </is>
       </c>
     </row>
@@ -1724,20 +1677,11 @@
         <is>
           <t>Anil stores his class's internal marks in a grid: each row is one student and each column is one subject. His teacher wants the same data flipped around — each row should be one subject instead — so Anil must swap the rows and columns. This flipped grid is called the transpose.
 Read the grid size `R` and `C`, then the `R` rows of the grid. Print the transpose: the first column of the original becomes the first row of the answer, the second column becomes the second row, and so on — giving `C` rows with `R` values each.
-### Input Format
-- Line 1: `R` and `C` separated by a space
-- Next `R` lines: `C` space-separated numbers each
-### Output Format
-```
-1 4
-2 5
-3 6
-```
 ### Example Walkthrough
 The sample grid has 2 rows and 3 columns: `1 2 3` and `4 5 6`. Its columns, read top to bottom, are (1, 4), (2, 5) and (3, 6), so the program prints the three lines `1 4`, `2 5` and `3 6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1893,10 +1837,10 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>r, c = map(int, input().split())
-grid = [list(map(int, input().split())) for _ in range(r)]
-for j in range(c):
-    row = [grid[i][j] for i in range(r)]
+          <t>r, c = map(int, input().split())   # grid dimensions
+grid = [list(map(int, input().split())) for _ in range(r)]   # read r rows into a nested list
+for j in range(c):   # each output row is one column of the original grid
+    row = [grid[i][j] for i in range(r)]   # collect column j across all rows
     print(*row)</t>
         </is>
       </c>
@@ -1911,17 +1855,11 @@
         <is>
           <t>A relay race results board records the finish order of runners as space-separated bib numbers on one line, and the announcer needs to quickly call out just the second-place runner's bib number.
 Write a program that reads a line of space-separated values and prints only the second value (the one at index 1).
-### Input Format
-- Line 1: Space-separated values
-### Output Format
-```
-2
-```
 ### Example Walkthrough
 In the sample, the line is `1 2 3`. Splitting it into a list gives `['1', '2', '3']`, and the second value (index 1) is `2`, which the program prints.
 ### Constraints
 - The input line has at least two space-separated values.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2053,7 +1991,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>print(input().split()[1])</t>
+          <t>print(input().split()[1])   # index 1 is the second value</t>
         </is>
       </c>
     </row>
@@ -2067,18 +2005,11 @@
         <is>
           <t>A shopping cart already holds a few item prices, and at checkout the cashier types in the price of one more item; the till needs the grand total including that last item.
 Write a program that reads a line of space-separated numbers into a list, reads one more number on the next line and appends it to the list, then prints the sum of the whole list.
-### Input Format
-- Line 1: Space-separated numbers (the existing cart)
-- Line 2: One more number (the item added at checkout)
-### Output Format
-```
-10
-```
 ### Example Walkthrough
 In the sample, the cart is `1 2 3` and the new item costs `4`. Appending 4 to the list gives `[1, 2, 3, 4]`, and summing it gives 10, so the program prints `10`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2217,280 +2148,86 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>p=list(map(int,input().split())); p.append(int(input())); print(sum(p))</t>
+          <t># read cart prices, append the checkout item, then print the total
+p=list(map(int,input().split())); p.append(int(input())); print(sum(p))</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Python - Sort by Marks</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>After the internal exams, Professor Rao wants a merit list pinned on the notice board: student names arranged from the highest scorer down to the lowest. If two students score the same, whoever appeared first in the register stays first.
 Read `N`, then `N` lines each containing a student's name and score. Print only the names, one per line, ordered from highest score to lowest. Students with equal scores keep their original input order.
-### Input Format
-- Line 1: `N`, the number of students
-- Next `N` lines: `name score`
-### Output Format
-```
-kabir
-asha
-meera
-```
 ### Example Walkthrough
 In the sample, `kabir` scored 95, `asha` scored 80 and `meera` scored 70. Ordering from highest to lowest score gives `kabir`, then `asha`, then `meera` — printed one name per line.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>list-methods</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O12" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>3
 asha 80
@@ -2498,43 +2235,43 @@
 meera 70</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>kabir
 asha
 meera</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>1
 sam 50</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>sam</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2
 a 10
 b 10</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>a
 b</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>4
 a 0
@@ -2543,7 +2280,7 @@
 d 50</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>b
 c
@@ -2551,20 +2288,20 @@
 a</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>2
 x -5
 y -10</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>x
 y</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>5
 p 60
@@ -2574,7 +2311,7 @@
 t 90</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>r
 t
@@ -2583,2983 +2320,2695 @@
 s</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>n = int(input())
 students = []
 for _ in range(n):
-    name, score = input().split()
-    students.append((name, int(score)))
-students.sort(key=lambda t: -t[1])
+    name, score = input().split()   # unpack name and score from the line
+    students.append((name, int(score)))   # store as a tuple
+students.sort(key=lambda t: -t[1])   # sort descending by score; stable sort keeps ties in original order
 for name, score in students:
     print(name)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Python - Adjacent Products</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Simran is setting a number puzzle for the class magazine. She writes a row of numbers and asks readers to build the next row by multiplying each pair of neighbours — the 1st number times the 2nd, the 2nd times the 3rd, and so on.
 Read a line of space-separated numbers and print the product of every adjacent (neighbouring) pair, in order, separated by spaces. A list of `N` numbers produces `N-1` products.
-### Input Format
-- Line 1: Space-separated numbers (at least two)
-### Output Format
-```
-2 6 12
-```
 ### Example Walkthrough
 The sample row is `1 2 3 4`. The neighbouring products are 1×2 = 2, 2×3 = 6 and 3×4 = 12, so the program prints `2 6 12`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>list-comprehensions</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O13" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>2 6 12</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>2 5</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>3 3 3</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>9 9</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>-1 -2 -3</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>2 6</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>1 1 1 1 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1 1 1 1</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>2 6 12 20 30 42 56 72 90</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-products = [nums[i] * nums[i + 1] for i in range(len(nums) - 1)]
+products = [nums[i] * nums[i + 1] for i in range(len(nums) - 1)]   # multiply each element with its neighbor
 print(*products)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Python - Cart Total</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>An online cart adds up the prices of the items in it. Read a line of space-separated prices and print their total.
-### Input Format
-- Line 1: Space-separated prices
-### Output Format
-```
-150
-```
 ### Example Walkthrough
 In the sample, the prices are `50 40 60`. Adding them gives `150`, so the program prints `150`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O14" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>10 20 30 40 50</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>-1 -2 3</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>0 0 0</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>-5 -10 -15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>-30</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>prices = list(map(int, input().split()))
-print(sum(prices))</t>
+print(sum(prices))   # sum() adds up all list elements</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Python - Item Count</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Read a line of space-separated values and print how many values there are.
-### Input Format
-- Line 1: Space-separated values
-### Output Format
-```
-5
-```
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A class representative's attendance app collects the roll numbers of every student present in the classroom as one space-separated line, and the representative just needs a quick headcount to report to the class teacher.
+Read a line of space-separated values and print how many values there are.
 ### Example Walkthrough
-In the sample, the input is `a b c d e`. It has `5` values, so the program prints `5`.
+The sample input is `3 1 4 1 5`. It has `5` values, so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O15" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>3 1 4 1 5</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>7 8 9 10</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>x x x</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>a b c d e f g h i j k l m n o</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>items = input().split()
-print(len(items))</t>
+print(len(items))   # len() gives the number of elements</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Python - Most Expensive</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Read a line of space-separated prices and print the largest one.
-### Input Format
-- Line 1: Space-separated prices
-### Output Format
-```
-55
-```
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>The hostel's kirana shop owner keys in the prices of items from today's delivery into a billing app so he can quickly spot the priciest item before restocking the shelf.
+Read a line of space-separated prices and print the largest one.
 ### Example Walkthrough
-In the sample, the prices are `20 55 30`. The largest is `55`, so the program prints `55`.
+The sample input is `10 55 30`. The largest price is `55`, so the program prints `55`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O16" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>10 55 30</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>-1 -9 -3</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>5 5 5</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>-100 100 0</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>prices = list(map(int, input().split()))
-print(max(prices))</t>
+print(max(prices))   # max() finds the largest value</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Python - Cheapest</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Read a line of space-separated prices and print the smallest one.
-### Input Format
-- Line 1: Space-separated prices
-### Output Format
-```
-10
-```
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>On the college's second-hand textbook marketplace group, several sellers post their asking prices for the same semester's textbook, and a budget-conscious student wants the app to instantly highlight the cheapest listing.
+Read a line of space-separated prices and print the smallest one.
 ### Example Walkthrough
-In the sample, the prices are `10 25 40`. The smallest is `10`, so the program prints `10`.
+The sample input is `10 55 30`. The smallest price is `10`, so the program prints `10`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O17" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>10 55 30</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>-1 -9 -3</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>5 5 5</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>-100 100 0</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>-100</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>prices = list(map(int, input().split()))
-print(min(prices))</t>
+print(min(prices))   # min() finds the smallest value</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Python - First Three</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>A leaderboard shows only the top three entries. Read a line of space-separated values and print the first three, separated by spaces (or all of them if there are fewer than three).
-### Input Format
-- Line 1: Space-separated values
-### Output Format
-```
-1 2 3
-```
 ### Example Walkthrough
 In the sample, the input is `1 2 3 4 5`. The first three values are `1`, `2`, and `3`, so the program prints `1 2 3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O18" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>9 8</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>9 8</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>a b c</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>a b c</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>a b c d e f g h</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>a b c</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>items = input().split()
-print(*items[:3])</t>
+print(*items[:3])   # slice keeps up to the first 3 items, even if fewer exist</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Python - Last Item</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Read a line of space-separated values and print the last one.
-### Input Format
-- Line 1: Space-separated values
-### Output Format
-```
-cherry
-```
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A college bus route app lists every stop on a driver's route in order, and the driver wants a quick way to check the final stop before starting the trip each morning.
+Read a line of space-separated values and print the last one.
 ### Example Walkthrough
-In the sample, the input is `apple banana cherry`. The last value is `cherry`, so the program prints `cherry`.
+The sample input is `apple banana cherry`. The last value is `cherry`, so the program prints `cherry`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O19" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>apple banana cherry</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>cherry</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>solo</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>solo</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>x y</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>y</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>a b c d e f g h i j</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>j</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>items = input().split()
-print(items[-1])</t>
+print(items[-1])   # negative index -1 refers to the last element</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Python - Tuple Swap</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>A seating app swaps the assigned seats of two passengers the moment they request an exchange, so passenger A gets passenger B's seat and vice versa.
 Write a program that reads two values on separate lines, swaps them, and prints the swapped values separated by a single space (second value first, then the first value).
-### Input Format
-- Line 1: First value
-- Line 2: Second value
-### Output Format
-```
-2 1
-```
 ### Example Walkthrough
 In the sample, the values are `1` and `2`. After swapping, the first holder now has `2` and the second holder has `1`, so the program prints `2 1`.
 ### Constraints
 - The inputs are valid values with no leading or trailing spaces.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>tuples</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O20" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>1
 2</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>2 1</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>A
 B</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>B A</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>left
 right</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>right left</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>hello
 world</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>world hello</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>5
 -1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>-1 5</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>x
 y</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>y x</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>x=input(); y=input(); x,y=y,x; print(x,y)</t>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>x=input(); y=input(); x,y=y,x; print(x,y)  # tuple unpacking swaps x and y without a temp variable</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Python - Sorted Copy</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>A photo-gallery app arranges uploaded photo IDs (given as space-separated numbers) in ascending order before displaying the thumbnail grid, so viewers always see photos in a predictable order.
 Write a program that reads a line of space-separated whole numbers and prints them sorted from smallest to largest, separated by single spaces.
-### Input Format
-- Line 1: Space-separated whole numbers
-### Output Format
-```
-1 2 3
-```
 ### Example Walkthrough
 In the sample, the numbers are `3 1 2`. Sorted from smallest to largest they become 1, 2, 3, so the program prints `1 2 3`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>list-methods</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O21" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>3 1 2</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>0 -1 10</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>-1 0 10</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>9 9 1</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>1 9 9</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>100 50 75</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>50 75 100</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>-3 -5 -1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>-5 -3 -1</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>8 6 7</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>6 7 8</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>print(*sorted(map(int,input().split())))</t>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>print(*sorted(map(int,input().split())))   # sorted() returns a new ascending list, original untouched</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Python - Count a Value</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Read a line of space-separated values, then a value to look for, and print how many times it appears in the list.
-### Input Format
-- Line 1: Space-separated values
-- Line 2: The value to count
-### Output Format
-```
-3
-```
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>During student council elections, ballots are entered as a line of candidate codes exactly as votes were cast, and the counting committee needs to know how many votes one particular candidate received.
+Read a line of space-separated values, then a value to look for, and print how many times it appears in the list.
 ### Example Walkthrough
-In the sample, the list is `a b a c a` and the target is `a`. It appears `3` times, so the program prints `3`.
+The sample list is `1 2 2 3 2` and the target is `2`. It appears `3` times, so the program prints `3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>list-methods</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O22" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>1 2 2 3 2
 2</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>a b c
 z</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>5 5 5
 5</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>a
 a</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>1 1 1 1 1
 1</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>x y z
 x</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>a b a b a b a
 b</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>items = input().split()
 target = input()
-print(items.count(target))</t>
+print(items.count(target))   # count() returns how many times target appears</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Python - Top Scores First</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Read a line of space-separated scores and print them sorted from highest to lowest, separated by spaces.
-### Input Format
-- Line 1: Space-separated scores
-### Output Format
-```
-5 4 3 1 1
-```
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>An online coding contest platform collects every participant's score at the end of the round and needs to display the leaderboard with the highest scorer listed first.
+Read a line of space-separated scores and print them sorted from highest to lowest, separated by spaces.
 ### Example Walkthrough
-In the sample, the scores are `3 1 4 1 5`. Sorted from highest to lowest they become `5, 4, 3, 1, 1`, so the program prints `5 4 3 1 1`.
+The sample scores are `3 1 4 1 5`. Sorted from highest to lowest they become `5 4 3 1 1`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>list-methods</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O23" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>3 1 4 1 5</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>5 4 3 1 1</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>10 20</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>20 10</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>-5 -1 -10</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>-1 -5 -10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>5 5 5</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>5 5 5</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>9 3 7 1 8 2 6 4 0 5</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>9 8 7 6 5 4 3 2 1 0</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-print(*sorted(nums, reverse=True))</t>
+print(*sorted(nums, reverse=True))   # reverse=True sorts from highest to lowest</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Python - Runner-Up Score</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Read a line of space-separated scores and print the second-highest distinct score.
-### Input Format
-- Line 1: Space-separated scores (at least two distinct values)
-### Output Format
-```
-5
-```
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>At the college sports day, the timing officials record every sprinter's score for the 100m dash, and the organizers want to announce the runner-up separately from the winner since ties can make the top score appear more than once.
+Read a line of space-separated scores and print the second-highest distinct score.
 ### Example Walkthrough
-In the sample, the scores are `5 8 5 3`. The distinct scores in descending order are `8, 5, 3`, so the second-highest is `5`, and the program prints `5`.
+The sample scores are `3 1 4 1 5 9`. The distinct scores in descending order are `9, 5, 4, 3, 1`, so the second-highest is `5`, and the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>list-methods</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O24" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>3 1 4 1 5 9</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>5 5 4</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>0 1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>-1 -2 -3</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>10 10 9</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>100 90 80 70 60</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-distinct = sorted(set(nums), reverse=True)
-print(distinct[1])</t>
+distinct = sorted(set(nums), reverse=True)   # set() drops duplicates before sorting descending
+print(distinct[1])   # index 1 is the second-highest distinct score</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Python - Keep the Evens</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Read a line of space-separated numbers and print only the even ones, in the same order, separated by spaces. Use a list comprehension.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-2 4 6
-```
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>The hostel warden's room-allocation sheet lists every room number in a wing, and the warden wants to quickly pull out just the even-numbered rooms, which are reserved for senior students, while keeping them in the original order.
+Read a line of space-separated numbers and print only the even ones, in the same order, separated by spaces. Use a list comprehension.
 ### Example Walkthrough
-In the sample, the numbers are `1 2 3 4 5 6`. The even ones, in order, are `2`, `4`, and `6`, so the program prints `2 4 6`.
+The sample numbers are `1 2 3 4 5 6`. The even ones, in order, are `2`, `4`, and `6`, so the program prints `2 4 6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>list-comprehensions</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O25" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>2 4 6</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>2 3 4</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>2 4</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>10 15 20</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>10 20</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>1 3 5 7</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>-2 -4 -1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>-2 -4</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>2 4 6 8 10</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG25" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-evens = [x for x in nums if x % 2 == 0]
+evens = [x for x in nums if x % 2 == 0]   # list comprehension with a filter condition
 print(*evens)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Python - Even-Index Sum</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Read a line of space-separated numbers and print the sum of the values at the even positions 0, 2, 4, and so on.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-90
-```
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>The canteen cashier logs the amount collected from every token sold during the day in order, and at closing time the manager wants to cross-check the till by adding up only every alternate entry starting from the first.
+Read a line of space-separated numbers and print the sum of the values at the even positions 0, 2, 4, and so on.
 ### Example Walkthrough
-In the sample, the numbers are `10 5 20 5 60`. The values at positions `0`, `2`, and `4` are `10`, `20`, and `60`, which sum to `90`, so the program prints `90`.
+The sample numbers are `10 20 30 40 50`. The values at positions `0`, `2`, and `4` are `10`, `30`, and `50`, which sum to `90`, so the program prints `90`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O26" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>10 20 30 40 50</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>-1 -2 -3 -4 -5</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-print(sum(nums[::2]))</t>
+print(sum(nums[::2]))   # step 2 slice picks every even index: 0, 2, 4, ...</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Python - Rotate Right by One</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Read a line of space-separated values and print them rotated one place to the right, so the last value moves to the front.
-### Input Format
-- Line 1: Space-separated values
-### Output Format
-```
-4 1 2 3
-```
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The hostel mess committee keeps a weekly cleaning duty roster listing students in order, and each week the schedule rotates so that whoever was last moves to the front for the next round.
+Read a line of space-separated values and print them rotated one place to the right, so the last value moves to the front.
 ### Example Walkthrough
-In the sample, the input is `1 2 3 4`. Moving the last value to the front gives `4 1 2 3`, which the program prints.
+The sample input is `1 2 3 4`. Moving the last value to the front gives `4 1 2 3`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O27" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>4 1 2 3</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>a b</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>b a</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>8 1 2 3 4 5 6 7</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>x y z</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>z x y</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>a b c d e f g h i j</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>j a b c d e f g h i</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>items = input().split()
-rotated = items[-1:] + items[:-1]
+rotated = items[-1:] + items[:-1]   # move the last element to the front
 print(*rotated)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Python - Position Finder</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Read a line of space-separated numbers, then a target. Print the 1-based position of the first time the target appears, or 0 if it does not appear.
-### Input Format
-- Line 1: Space-separated numbers
-- Line 2: The target
-### Output Format
-```
-2
-```
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>The college library's catalog app stores accession numbers of books on a shelf in the order they are arranged, and a librarian wants to quickly look up where a particular book code sits on the shelf without walking down the aisle.
+Read a line of space-separated numbers, then a target. Print the 1-based position of the first time the target appears, or 0 if it does not appear.
 ### Example Walkthrough
-In the sample, the numbers are `5 3 8` and the target is `3`. It first appears at 1-based position `2`, so the program prints `2`.
+The sample numbers are `10 20 30` and the target is `20`. It first appears at 1-based position `2`, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>list-methods</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O28" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>10 20 30
 20</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>1 2 3
 5</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>5 5 5
 5</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>-1 -2 -3
 -2</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>1 2 3 2 1
 2</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10
 10</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 target = int(input())
 if target in nums:
-    print(nums.index(target) + 1)
+    print(nums.index(target) + 1)   # index() gives 0-based position; +1 makes it 1-based
 else:
-    print(0)</t>
+    print(0)   # not found</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Python - Even List</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>A raffle organizer wants to filter a submitted list of ticket numbers down to just the even-numbered tickets, since only even tickets qualify for the bonus draw.
 Write a program that reads a line of space-separated whole numbers and prints only the even ones, in their original order, separated by single spaces. If none are even, print an empty line.
-### Input Format
-- Line 1: Space-separated whole numbers
-### Output Format
-```
-2 4
-```
 ### Example Walkthrough
 In the sample, the numbers are `1 2 3 4`. Checking each one, 2 and 4 are even while 1 and 3 are not, so the program prints `2 4`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>list-comprehensions</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O29" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>2 4</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>5 7</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>0 2 4</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>0 2 4</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>-2 -1 3</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>10 11 12</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>10 12</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>8 8 9</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>8 8</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>nums=list(map(int,input().split())); print(*[x for x in nums if x%2==0])</t>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>nums=list(map(int,input().split())); print(*[x for x in nums if x%2==0])  # filter comprehension keeps only even numbers</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Python - Nested Row Sums</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>A spreadsheet-style grade sheet stores each student's row of assignment scores on its own line, and the teacher wants the row total printed for every student, one total per line, in the order they appear.
 Write a program that reads a whole number R (the number of students), then reads R lines each containing space-separated scores, and prints the sum of each row's scores on its own line.
-### Input Format
-- Line 1: R, the number of rows
-- Next R lines: space-separated numbers for that row
-### Output Format
-```
-3
-7
-```
 ### Example Walkthrough
 In the sample, R is 2, the first row is `1 2` (sum 3) and the second row is `3 4` (sum 7), so the program prints `3` then `7`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>nested-lists</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O30" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>2
 1 2
 3 4</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>3
 7</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>1
 5 5</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>3
 1
@@ -5567,51 +5016,51 @@
 3</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>1
 2
 3</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>2
 0 0
 1 1</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>0
 2</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>2
 -1 2
 3 -4</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>1
 -1</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>1
 10 20 30</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>3
 1 1
@@ -5619,474 +5068,275 @@
 3 3</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>2
 4
 6</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>r=int(input())
-for _ in range(r): print(sum(map(int,input().split())))</t>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>r=int(input())   # number of student rows
+for _ in range(r): print(sum(map(int,input().split())))   # sum each row's scores as it is read</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Python - Pair Products</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>An invoice calculator works out the amount for every line item by multiplying each item's quantity by its unit price, given as two parallel lists: quantities on the first line and prices on the second.
 Write a program that reads two lines of space-separated whole numbers of equal length, multiplies each pair of values at the same position together, and prints the results separated by single spaces.
-### Input Format
-- Line 1: Space-separated quantities
-- Line 2: Space-separated prices (same count as quantities)
-### Output Format
-```
-4 10 18
-```
 ### Example Walkthrough
 In the sample, the quantities are `1 2 3` and the prices are `4 5 6`. Multiplying each pair gives 1x4=4, 2x5=10, and 3x6=18, so the program prints `4 10 18`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>sequence-iteration</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O31" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>1 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>4 10 18</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>2
 3</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>0 1
 5 6</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>0 6</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>-1 2
 3 -4</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>-3 -8</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>10 20
 1 2</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>10 40</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>1 1 1
 9 8 7</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>9 8 7</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>5 6 7
 0 1 2</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>0 6 14</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>a=list(map(int,input().split())); b=list(map(int,input().split())); print(*[x*y for x,y in zip(a,b)])</t>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>a=list(map(int,input().split())); b=list(map(int,input().split())); print(*[x*y for x,y in zip(a,b)])  # zip() pairs elements at the same position</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Python - Column Sums</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Read a grid with `R` rows and `C` columns and print the sum of each column on one line, separated by spaces.
-### Input Format
-- Line 1: R and C separated by a space
-- Next R lines: C space-separated numbers each
-### Output Format
-```
-5 7 9
-```
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A college store room arranges cartons on shelving in a grid of rows and columns, and the storekeeper needs the total number of items in each column to know how much stock sits on every shelf column.
+Read a grid with `R` rows and `C` columns and print the sum of each column on one line, separated by spaces.
 ### Example Walkthrough
-In the sample, the grid is `2` rows by `3` columns: `1 2 3` and `4 5 6`. The column sums are `1 + 4 = 5`, `2 + 5 = 7`, and `3 + 6 = 9`, so the program prints `5 7 9`.
+The sample grid is `2` rows by `3` columns: `1 2 3` and `4 5 6`. The column sums are `1 + 4 = 5`, `2 + 5 = 7`, and `3 + 6 = 9`, so the program prints `5 7 9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>nested-lists</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O32" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>2 3
 1 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>5 7 9</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>1 1
 7</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>3 2
 1 1
@@ -6094,35 +5344,35 @@
 3 3</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>6 6</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>1 4
 1 2 3 4</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>2 2
 -1 -2
 -3 -4</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>-4 -6</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>4 1
 1
@@ -6131,12 +5381,12 @@
 4</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>3 3
 1 2 3
@@ -6144,124 +5394,118 @@
 7 8 9</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>12 15 18</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>r, c = map(int, input().split())
-grid = [list(map(int, input().split())) for _ in range(r)]
-sums = [sum(grid[i][j] for i in range(r)) for j in range(c)]
+grid = [list(map(int, input().split())) for _ in range(r)]   # nested list: one list per row
+sums = [sum(grid[i][j] for i in range(r)) for j in range(c)]   # for each column j, sum down all rows
 print(*sums)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Python - Flatten the Rows</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Read `R` rows, each a line of space-separated numbers of any length, and print all the numbers on a single line, separated by spaces, in order.
-### Input Format
-- Line 1: R, the number of rows
-- Next R lines: space-separated numbers each
-### Output Format
-```
-1 2 3 4 5
-```
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A placement cell's report generator stores each recruiter's shortlisted roll numbers on a separate row, and before exporting the final report the tool needs every roll number combined onto a single line in the order they were collected.
+Read `R` rows, each a line of space-separated numbers of any length, and print all the numbers on a single line, separated by spaces, in order.
 ### Example Walkthrough
-In the sample, `R` is `2` with rows `1 2 3` and `4 5`. Combined in order, they form `1 2 3 4 5`, which the program prints.
+The sample has `R` as `2` with rows `1 2` and `3 4 5`. Combined in order, they form `1 2 3 4 5`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>nested-lists</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O33" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>2
 1 2
 3 4 5</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>1
 9</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>3
 1
@@ -6269,28 +5513,28 @@
 3</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>1
 1 2 3 4 5 6 7</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>4
 1
@@ -6299,114 +5543,108 @@
 7</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>2
 1 2 3 4 5
 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE33" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG33" t="inlineStr">
         <is>
           <t>r = int(input())
 flat = []
 for _ in range(r):
-    flat += input().split()
+    flat += input().split()   # += extends the list with each row's values
 print(*flat)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Python - Diagonal Sum</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Read a square grid of size `N` and print the sum of the values on its main diagonal (top-left to bottom-right).
-### Input Format
-- Line 1: N
-- Next N lines: N space-separated numbers each
-### Output Format
-```
-15
-```
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>A multiplex's booking system arranges every screen's seats in a grid of rows and columns, and the premium seats form a diagonal line from the front-left corner to the back-right corner; the manager wants their total ticket value.
+Read a square grid of size `N` and print the sum of the values on its main diagonal (top-left to bottom-right).
 ### Example Walkthrough
-In the sample, `N` is `3` with rows `1 2 3`, `4 5 6`, and `7 8 9`. The diagonal values are `1`, `5`, and `9`, which sum to `15`, so the program prints `15`.
+The sample has `N` as `3` with rows `1 2 3`, `4 5 6`, and `7 8 9`. The diagonal values are `1`, `5`, and `9`, which sum to `15`, so the program prints `15`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>nested-lists</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O34" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>3
 1 2 3
@@ -6414,46 +5652,46 @@
 7 8 9</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>1
 5</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>2
 1 2
 3 4</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>1
 0</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>4
 1 0 0 0
@@ -6462,24 +5700,24 @@
 0 0 0 4</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>2
 -1 -2
 -3 -4</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>5
 1 2 3 4 5
@@ -6489,150 +5727,143 @@
 21 22 23 24 25</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>n = int(input())
 grid = [list(map(int, input().split())) for _ in range(n)]
-total = sum(grid[i][i] for i in range(n))
+total = sum(grid[i][i] for i in range(n))   # grid[i][i] is the diagonal element of row i
 print(total)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Python - Row Maximums</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Read a grid with `R` rows and `C` columns and print the largest value in each row, one per line, top to bottom.
-### Input Format
-- Line 1: R and C separated by a space
-- Next R lines: C space-separated numbers each
-### Output Format
-```
-9
-8
-```
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A cricket scoreboard app records the runs scored off each ball for every over in a grid, one over per row, and the commentator wants the best ball of each over printed out for the highlights reel.
+Read a grid with `R` rows and `C` columns and print the largest value in each row, one per line, top to bottom.
 ### Example Walkthrough
-In the sample, the grid is `2` rows by `3` columns: `3 9 5` and `8 2 1`. The largest value in the first row is `9` and in the second row is `8`, so the program prints `9` then `8`.
+The sample grid is `2` rows by `3` columns: `1 9 3` and `4 2 8`. The largest value in the first row is `9` and in the second row is `8`, so the program prints `9` then `8`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>nested-lists</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O35" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>2 3
 1 9 3
 4 2 8</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>9
 8</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>1 1
 7</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>2 2
 -1 -2
 -3 -4</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>-1
 -3</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>1 4
 1 2 3 4</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>3 1
 5
@@ -6640,27 +5871,27 @@
 8</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>5
 2
 8</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>2 2
 0 0
 0 0</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>4 3
 1 2 3
@@ -6669,7 +5900,7 @@
 10 11 12</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>3
 6
@@ -6677,167 +5908,160 @@
 12</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG35" t="inlineStr">
         <is>
           <t>r, c = map(int, input().split())
 for _ in range(r):
     row = list(map(int, input().split()))
-    print(max(row))</t>
+    print(max(row))   # largest value in this row</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Python - Value Counts</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Read a line of space-separated numbers and, for each distinct value in ascending order, print the value and how many times it appears in the form 'value:count', one per line.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-1:1
-2:2
-3:3
-```
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>The college fest's merchandise stall records the T-shirt size code chosen by every student who placed an order, and before placing the bulk order the organizers need a clean summary of how many shirts of each size to print.
+Read a line of space-separated numbers and, for each distinct value in ascending order, print the value and how many times it appears in the form 'value:count', one per line.
 ### Example Walkthrough
-In the sample, the numbers are `1 2 2 3 3 3`. The distinct values in ascending order are `1`, `2`, and `3`, appearing `1`, `2`, and `3` times respectively, so the program prints `1:1`, `2:2`, and `3:3`.
+The sample numbers are `1 2 2 3 3 3`. The distinct values in ascending order are `1`, `2`, and `3`, appearing `1`, `2`, and `3` times respectively, so the program prints `1:1`, `2:2`, and `3:3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>list-methods</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O36" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>1 2 2 3 3 3</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>1:1
 2:2
 3:3</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>5 5</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>5:2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>3 1 2</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>1:1
 2:1
 3:1</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>-1 -1 -2</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>-2:1
 -1:2</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>7 7 7 7 7</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>7:5</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>1:1
 2:1
@@ -6851,620 +6075,594 @@
 10:1</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-for v in sorted(set(nums)):
-    print(f"{v}:{nums.count(v)}")</t>
+for v in sorted(set(nums)):   # unique values, visited in ascending order
+    print(f"{v}:{nums.count(v)}")   # count() gives occurrences of each value</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Python - Two-Sum Positions</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Read a line of space-separated numbers and a target. Print the 1-based positions of the first pair of values (earlier position first) that add up to the target, separated by a space. Print 'None' if there is no such pair.
-### Input Format
-- Line 1: Space-separated numbers
-- Line 2: Target
-### Output Format
-```
-1 2
-```
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A vending machine in the hostel corridor lists the denominations available in its coin tray in order, and it needs to find the first pair of coins (checking earlier positions first) that together make up the exact change requested.
+Read a line of space-separated numbers and a target. Print the 1-based positions of the first pair of values (earlier position first) that add up to the target, separated by a space. Print 'None' if there is no such pair.
 ### Example Walkthrough
-In the sample, the numbers are `2 7 11 15` and the target is `9`. The first pair that adds up to `9` is `2` and `7`, at 1-based positions `1` and `2`, so the program prints `1 2`.
+The sample numbers are `2 7 11 15` and the target is `9`. The first pair that adds up to `9` is `2` and `7`, at 1-based positions `1` and `2`, so the program prints `1 2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O37" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>2 7 11 15
 9</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>1 2 3
 7</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>3 3
 6</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>0 0
 0</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>-1 -2 -3
 -5</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>2 3</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>5 5 5 5
 10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10
 19</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>9 10</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG37" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 target = int(input())
-found = None
+found = None   # will hold the matching pair's positions
 for i in range(len(nums)):
-    for j in range(i + 1, len(nums)):
+    for j in range(i + 1, len(nums)):   # only check pairs after i, so each pair is checked once
         if nums[i] + nums[j] == target:
-            found = (i + 1, j + 1)
+            found = (i + 1, j + 1)   # store as 1-based positions
             break
     if found:
-        break
+        break   # stop the outer loop once a pair is found
 print(f"{found[0]} {found[1]}" if found else "None")</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Python - Common Elements</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Read two lines of space-separated values. Print the values that appear in both lists, in the order they appear in the first list, separated by spaces (each common value once).
-### Input Format
-- Line 1: First list
-- Line 2: Second list
-### Output Format
-```
-2 4
-```
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>The academic office collects the elective subject codes chosen by two different sections, and the timetable coordinator needs to know which electives were picked by students in both sections so a common time slot can be blocked.
+Read two lines of space-separated values. Print the values that appear in both lists, in the order they appear in the first list, separated by spaces (each common value once).
 ### Example Walkthrough
-In the sample, the lists are `1 2 3 4` and `2 4 6`. The values `2` and `4` appear in both, in the order they appear in the first list, so the program prints `2 4`.
+The sample lists are `1 2 3 4` and `2 4 6`. The values `2` and `4` appear in both, in the order they appear in the first list, so the program prints `2 4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>lists</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O38" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P38" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>1 2 3 4
 2 4 6</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>2 4</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>5 6 7
 6 7 8</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>6 7</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>1 2
 2 1</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>a
 a</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>1 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>x x y y
 y x</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>x y</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10
 2 4 6 8 10 12</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE38" t="inlineStr">
         <is>
           <t>2 4 6 8 10</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG38" t="inlineStr">
         <is>
           <t>a = input().split()
 b = input().split()
 result = []
 for x in a:
-    if x in b and x not in result:
+    if x in b and x not in result:   # keep values present in both lists, without duplicates
         result.append(x)
 print(*result)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Python - Rotate Left</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>A round-robin duty scheduler rotates a list of employee names to the left by however many days have passed, so a different person starts the queue each day, wrapping back to the beginning once everyone has had a turn.
 Write a program that reads a line of space-separated names, reads a whole number K on the next line, and prints the list rotated left by K positions (using K modulo the number of names, so rotating past the end wraps around).
-### Input Format
-- Line 1: Space-separated names
-- Line 2: K, the number of positions to rotate left
-### Output Format
-```
-b c d a
-```
 ### Example Walkthrough
 In the sample, the names are `a b c d` and K is 1. Rotating left by 1 moves `a` to the end, giving `b c d a`, which the program prints.
 ### Constraints
 - The input names contain no spaces within a single name.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>list-methods</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O39" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>a b c d
 1</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>b c d a</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>1 2 3
 2</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>3 1 2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>x
 5</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>p q r
 0</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>p q r</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>1 2 3 4 5
 7</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>3 4 5 1 2</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>A B
 3</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>B A</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>red blue green
 2</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE39" t="inlineStr">
         <is>
           <t>green red blue</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>items=input().split(); k=int(input())%len(items); print(*(items[k:]+items[:k]))</t>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>items=input().split(); k=int(input())%len(items); print(*(items[k:]+items[:k]))  # modulo wraps K past the list length; slicing rotates left</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Python - Matrix Diagonal</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>A venue's seating chart is laid out as a square grid of seat numbers, and the manager wants to know the total of just the diagonal seats (row 1 seat 1, row 2 seat 2, and so on) reserved for VIP placement.
 Write a program that reads a whole number N, then reads N lines each with N space-separated numbers forming a square grid, and prints the sum of the diagonal values (the value at row `i`, column `i`, for each row).
-### Input Format
-- Line 1: N, the size of the grid
-- Next N lines: N space-separated numbers each
-### Output Format
-```
-5
-```
 ### Example Walkthrough
 In the sample, N is 2 and the grid is `1 2` then `3 4`. The diagonal values are the first row's first value (1) and the second row's second value (4), which sum to 5, so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>nested-lists</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O40" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>1</v>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>2
 1 2
 3 4</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>1
 5</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>3
 1 0 0
@@ -7472,24 +6670,24 @@
 0 0 3</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>2
 -1 2
 3 -4</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>3
 1 2 3
@@ -7497,12 +6695,12 @@
 7 8 9</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>4
 1 0 0 0
@@ -7511,113 +6709,106 @@
 0 0 0 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>2
 0 0
 0 0</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>n=int(input()); total=0
-for i in range(n): total+=list(map(int,input().split()))[i]
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>n=int(input()); total=0   # total accumulates the diagonal sum
+for i in range(n): total+=list(map(int,input().split()))[i]   # index i picks the diagonal value in row i
 print(total)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Python - Tuple Grade Sort</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>A sports day results board lists each participant's name and score as they are submitted, and needs to display the final ranking from highest score to lowest, keeping the original entry order when two participants tie.
 Write a program that reads a whole number N, then reads N lines each with a name and a score separated by a space, and prints just the names in order from highest score to lowest, separated by single spaces.
-### Input Format
-- Line 1: N, the number of participants
-- Next N lines: name and score separated by a space
-### Output Format
-```
-Meena Asha Rohan
-```
 ### Example Walkthrough
 In the sample, N is 3 with Asha scoring 90, Rohan scoring 80, and Meena scoring 95. Ranking from highest to lowest score gives Meena (95), Asha (90), Rohan (80), so the program prints `Meena Asha Rohan`.
 ### Constraints
 - Names contain no spaces, and scores are valid whole numbers.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>lists-and-tuples</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>tuples</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O41" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>3
 Asha 90
@@ -7625,35 +6816,35 @@
 Meena 95</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>Meena Asha Rohan</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>1
 A 10</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>2
 X 5
 Y 5</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>X Y</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>3
 A 1
@@ -7661,24 +6852,24 @@
 C 2</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>B C A</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>2
 Dev 100
 Zoya 99</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>Dev Zoya</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>4
 a 4
@@ -7687,30 +6878,30 @@
 d 2</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>a c d b</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>2
 Low -1
 High 0</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE41" t="inlineStr">
         <is>
           <t>High Low</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>n=int(input()); rec=[]
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>n=int(input()); rec=[]   # rec stores (name, score) tuples
 for _ in range(n):
- name,score=input().split(); rec.append((name,int(score)))
-rec.sort(key=lambda x:x[1], reverse=True)
-print(*[x[0] for x in rec])</t>
+ name,score=input().split(); rec.append((name,int(score)))   # pack each entry as a tuple
+rec.sort(key=lambda x:x[1], reverse=True)   # sort descending by score, stable so ties keep original order
+print(*[x[0] for x in rec])   # extract just the names after sorting</t>
         </is>
       </c>
     </row>
